--- a/03_Cluster_groups/Muscle_strength/04_Set_Contrasts/c_data/set_contrasts.xlsx
+++ b/03_Cluster_groups/Muscle_strength/04_Set_Contrasts/c_data/set_contrasts.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11461" uniqueCount="3078">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11458" uniqueCount="3076">
   <si>
     <t>sheet</t>
   </si>
@@ -8786,7 +8786,7 @@
     <t>01_Trunk/04_Gene_Sets/c_data/gene_sets.rds</t>
   </si>
   <si>
-    <t>587e179734739b4ba3ccdf9a51c3f6c0</t>
+    <t>bc1bf66e89df936e164c317354990470</t>
   </si>
   <si>
     <t>fit</t>
@@ -9249,12 +9249,6 @@
   </si>
   <si>
     <t>3.0.2</t>
-  </si>
-  <si>
-    <t>writexl</t>
-  </si>
-  <si>
-    <t>2.0.1</t>
   </si>
 </sst>
 </file>
@@ -75580,7 +75574,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C72"/>
+  <dimension ref="A1:C71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -76364,17 +76358,6 @@
         <v>2941</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
-      <c r="A72" t="s">
-        <v>3076</v>
-      </c>
-      <c r="B72" t="s">
-        <v>3077</v>
-      </c>
-      <c r="C72" t="s">
-        <v>3044</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/03_Cluster_groups/Muscle_strength/04_Set_Contrasts/c_data/set_contrasts.xlsx
+++ b/03_Cluster_groups/Muscle_strength/04_Set_Contrasts/c_data/set_contrasts.xlsx
@@ -8783,7 +8783,7 @@
     <t>gene_sets</t>
   </si>
   <si>
-    <t>01_Trunk/04_Gene_Sets/c_data/gene_sets.rds</t>
+    <t>01_Processing/04_Gene_Sets/c_data/gene_sets.rds</t>
   </si>
   <si>
     <t>bc1bf66e89df936e164c317354990470</t>
@@ -8795,7 +8795,7 @@
     <t>03_Cluster_groups/Muscle_strength/03_Protein_Contrasts/c_data/fit.rds</t>
   </si>
   <si>
-    <t>4b3d729be71f7a7648f18f8a521ccc88</t>
+    <t>293a41d7ef36de7179b42dc1f593e3d3</t>
   </si>
   <si>
     <t>design</t>
@@ -8804,22 +8804,22 @@
     <t>03_Cluster_groups/Muscle_strength/02_Design_Contrasts/c_data/design.rds</t>
   </si>
   <si>
-    <t>7257669772ab17add4fbd88a7b4981d0</t>
-  </si>
-  <si>
-    <t>03_Cluster_groups/Muscle_strength/01_Clustering/c_data/inputs/DAList_limpa.rds</t>
-  </si>
-  <si>
-    <t>f650266fc408e16f3363512e5866142c</t>
+    <t>c0cfb05785ba25feadb966caf1fa5a50</t>
+  </si>
+  <si>
+    <t>01_Processing/03_Quantification/c_data/DAList_limpa.rds</t>
+  </si>
+  <si>
+    <t>268362b9975bc00d3bc3b85b0f5736f7</t>
   </si>
   <si>
     <t>singscore</t>
   </si>
   <si>
-    <t>03_Cluster_groups/Muscle_strength/01_Clustering/c_data/inputs/singscore.rds</t>
-  </si>
-  <si>
-    <t>768c2a055a54131baabba7bd088cd1f7</t>
+    <t>01_Processing/05_Set_Scores/c_data/singscore.rds</t>
+  </si>
+  <si>
+    <t>4f1249d3e2d6782468d2836f84bdc76a</t>
   </si>
   <si>
     <t>phenotype</t>
